--- a/Exchange_matrix.xlsx
+++ b/Exchange_matrix.xlsx
@@ -418,2243 +418,2243 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>2.137960296633624</v>
+        <v>4.892897641955348</v>
       </c>
       <c r="B1" t="n">
-        <v>0.3481926055365411</v>
+        <v>0.6020427689199894</v>
       </c>
       <c r="C1" t="n">
-        <v>0.3022935791267981</v>
+        <v>0.5509422834429198</v>
       </c>
       <c r="D1" t="n">
-        <v>-0.4526212491134798</v>
+        <v>-1.354430167351911e-16</v>
       </c>
       <c r="E1" t="n">
-        <v>-0.146227632944669</v>
+        <v>2.815349946227869e-16</v>
       </c>
       <c r="F1" t="n">
-        <v>0.3393477554506545</v>
+        <v>0.01091640483058394</v>
       </c>
       <c r="G1" t="n">
-        <v>-0.1340973179705463</v>
+        <v>4.676118570489135e-18</v>
       </c>
       <c r="H1" t="n">
-        <v>-0.07398266543704776</v>
+        <v>8.803788737159261e-17</v>
       </c>
       <c r="I1" t="n">
-        <v>0.2209550199877435</v>
+        <v>0.007583869721333462</v>
       </c>
       <c r="J1" t="n">
-        <v>-0.04328927832703032</v>
+        <v>2.277793963904285e-05</v>
       </c>
       <c r="K1" t="n">
-        <v>-0.03724049206029539</v>
+        <v>6.180821462041259e-05</v>
       </c>
       <c r="L1" t="n">
-        <v>-0.05747273379986545</v>
+        <v>0.004361067254289353</v>
       </c>
       <c r="M1" t="n">
-        <v>0.01438312874804778</v>
+        <v>-3.39784255169843e-17</v>
       </c>
       <c r="N1" t="n">
-        <v>0.04793011673866256</v>
+        <v>-2.552522888200458e-18</v>
       </c>
       <c r="O1" t="n">
-        <v>0.02078350983047048</v>
+        <v>-0.0003405241634013811</v>
       </c>
       <c r="P1" t="n">
-        <v>0.007514102544864027</v>
+        <v>-1.373830487826963e-17</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.04260902357998272</v>
+        <v>2.786025309177217e-18</v>
       </c>
       <c r="R1" t="n">
-        <v>0.149787302087932</v>
+        <v>-0.01792337552459341</v>
       </c>
       <c r="S1" t="n">
-        <v>0.01722100174373189</v>
+        <v>0.0007840850690434835</v>
       </c>
       <c r="T1" t="n">
-        <v>-0.05284167274158993</v>
+        <v>0.09247052547881411</v>
       </c>
       <c r="U1" t="n">
-        <v>0.1751108644916988</v>
+        <v>0.1801314987180108</v>
       </c>
       <c r="V1" t="n">
-        <v>0.09857334360723928</v>
+        <v>4.440135491939364e-17</v>
       </c>
       <c r="W1" t="n">
-        <v>0.1340388185222633</v>
+        <v>-1.162737942979774e-17</v>
       </c>
       <c r="X1" t="n">
-        <v>-1.267853816709839</v>
+        <v>-0.1815834160200568</v>
       </c>
       <c r="Y1" t="n">
-        <v>-0.0561435912350044</v>
+        <v>2.239209142907633e-17</v>
       </c>
       <c r="Z1" t="n">
-        <v>-0.02060803788629982</v>
+        <v>2.803191920560972e-17</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.2100887004266605</v>
+        <v>-0.312330366275808</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3481926055365404</v>
+        <v>0.6020427689199895</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1077632548438556</v>
+        <v>1.136245798867491</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2923189288207557</v>
+        <v>0.7882964655447114</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1217100564806427</v>
+        <v>9.442785887086032e-16</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07308689929308358</v>
+        <v>-4.303859865047948e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2240073741344081</v>
+        <v>0.02573815672236112</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.103833856217659</v>
+        <v>8.625690341707752e-16</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09331776170357003</v>
+        <v>-7.231842128405798e-17</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4360104670071036</v>
+        <v>0.01231159413127005</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02872242804301312</v>
+        <v>6.180821462039969e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.04797128363389092</v>
+        <v>0.001107141381953388</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4750539649665784</v>
+        <v>0.01956225489473925</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02665035994122677</v>
+        <v>1.575327589092172e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02049980313820799</v>
+        <v>2.375682626075259e-17</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05573856886858204</v>
+        <v>0.0007795331999253442</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3413649377313675</v>
+        <v>-6.245707984660922e-17</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8196874487134383</v>
+        <v>9.997634617281538e-17</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6049677143131581</v>
+        <v>-0.0653639768085742</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04005452720909816</v>
+        <v>0.02805835971472784</v>
       </c>
       <c r="T2" t="n">
-        <v>0.710331228100053</v>
+        <v>0.2412860034848959</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4776895950143675</v>
+        <v>0.3255764581112063</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8434180300837161</v>
+        <v>-6.482093157361337e-16</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1356721416658285</v>
+        <v>5.768805169174925e-16</v>
       </c>
       <c r="X2" t="n">
-        <v>4.679948070618551</v>
+        <v>-0.3794276433736798</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.08099713667798128</v>
+        <v>3.112702011111816e-16</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.08427155490673993</v>
+        <v>-6.353841898545101e-17</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.204350177292082</v>
+        <v>-0.5029630951101126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3022935791267983</v>
+        <v>0.5509422834429196</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2923189288207557</v>
+        <v>0.7882964655447112</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.099697635355238</v>
+        <v>0.5646529090313922</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1080107079984575</v>
+        <v>-1.70925271373994e-15</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0992059998115931</v>
+        <v>6.53962303214587e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4764211869457381</v>
+        <v>0.066636768707432</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0568663329187504</v>
+        <v>-2.874843147613067e-16</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.09852476325808862</v>
+        <v>2.837392631988946e-16</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8606167382878851</v>
+        <v>0.04627785265144606</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03388596415441433</v>
+        <v>0.004361067254289369</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4404924893086682</v>
+        <v>0.01956225489473864</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.123511616385507</v>
+        <v>0.03208826254075765</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1324986389563614</v>
+        <v>8.421612013601287e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1874553085332433</v>
+        <v>-7.767699621681544e-17</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8825511133401215</v>
+        <v>-0.02090546578538786</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3890245181911434</v>
+        <v>2.481454031533025e-16</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006243368851932662</v>
+        <v>3.225396626733715e-17</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.148854857467976</v>
+        <v>-0.06971860414654689</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2128292681003968</v>
+        <v>0.1741267691783683</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7585243655546625</v>
+        <v>0.2027236723366815</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.555173260730673</v>
+        <v>0.2550843692736627</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6841530643549891</v>
+        <v>-4.626781688552991e-16</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4648977372355639</v>
+        <v>3.527770665191413e-16</v>
       </c>
       <c r="X3" t="n">
-        <v>2.357502712755823</v>
+        <v>-0.2801140382758386</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1855838638663503</v>
+        <v>6.783164846643276e-17</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1735964690947603</v>
+        <v>3.557803605218208e-17</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.336006789121666</v>
+        <v>-0.3500064536573373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.4526212491134794</v>
+        <v>-1.354430167351902e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1217100564806427</v>
+        <v>9.442785887086091e-16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1080107079984577</v>
+        <v>-1.70925271373994e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5119389490337167</v>
+        <v>1.190976243486322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0128586842953342</v>
+        <v>-1.140283495018604e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05242515380741527</v>
+        <v>1.407374699646843e-14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2671544752770684</v>
+        <v>0.4376621253113825</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02436939411494165</v>
+        <v>3.612703095021171e-16</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.001574027429646388</v>
+        <v>1.513161191880386e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02014829926358701</v>
+        <v>-1.137027338551851e-17</v>
       </c>
       <c r="K4" t="n">
-        <v>1.042983688310378e-05</v>
+        <v>9.342625539767645e-17</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1258493323505711</v>
+        <v>-2.803182876057858e-17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06384140613802622</v>
+        <v>-0.0001311157213853511</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03239423413150067</v>
+        <v>3.359394555427065e-17</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.002568101092617354</v>
+        <v>1.122219968897035e-15</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1705338143143499</v>
+        <v>0.01079237245975019</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08641481815868829</v>
+        <v>5.093672435854771e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.08298628647109868</v>
+        <v>9.678401045599814e-16</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009347721661147522</v>
+        <v>-7.104945111132761e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1280226980225189</v>
+        <v>-3.247762197431186e-15</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06995697083609854</v>
+        <v>-1.454720075916618e-15</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.08988831917730881</v>
+        <v>0.1135229257250884</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0749727992759153</v>
+        <v>2.427842827781269e-15</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04652939776438739</v>
+        <v>8.394861729787419e-15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05558051159775832</v>
+        <v>0.1439004977286862</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1130759083614428</v>
+        <v>1.087915168824748e-15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1399306999868982</v>
+        <v>3.288546787631615e-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.146227632944669</v>
+        <v>2.815349946227881e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.07308689929308358</v>
+        <v>-4.303859865047934e-16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.09920599981159316</v>
+        <v>6.539623032145832e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0128586842953342</v>
+        <v>-1.140283495018604e-15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7823004458582197</v>
+        <v>1.190976243486318</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01827446424268615</v>
+        <v>-5.070753105114011e-15</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02995141294299221</v>
+        <v>-3.157797440379332e-16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3352027858612803</v>
+        <v>0.4376621253113822</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00495180921913398</v>
+        <v>-1.862977378644034e-15</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.03767921008082036</v>
+        <v>6.117445103472961e-17</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01198441457787414</v>
+        <v>-8.717649081767181e-19</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1532876190780578</v>
+        <v>1.823458690930504e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01155220301451595</v>
+        <v>-2.478403481261462e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03934127170063008</v>
+        <v>-0.0001311157213856192</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05185808020567099</v>
+        <v>-4.184121362838132e-16</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1305030129462645</v>
+        <v>4.806723473979158e-16</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5093852048291792</v>
+        <v>0.01079237245975032</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04003145009089139</v>
+        <v>-5.316011823962527e-16</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05836804347281761</v>
+        <v>1.968867188832426e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3361638313409375</v>
+        <v>1.031565610655225e-15</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1414267378950517</v>
+        <v>3.915137501783903e-16</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2624065950466219</v>
+        <v>2.389715389611257e-15</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3676672279970428</v>
+        <v>0.1135229257250923</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6532567243171628</v>
+        <v>-3.591005271356499e-15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3124212471220639</v>
+        <v>8.176479522531827e-16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4130051094565373</v>
+        <v>0.1439004977286873</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4416675868065112</v>
+        <v>-2.376062801743562e-15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.3393477554506547</v>
+        <v>0.01091640483058389</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2240073741344082</v>
+        <v>0.02573815672236101</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.4764211869457379</v>
+        <v>0.06663676870743199</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05242515380741525</v>
+        <v>1.407374699646844e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01827446424268617</v>
+        <v>-5.070753105114009e-15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3042577187518527</v>
+        <v>1.039353250703643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.117836380052036</v>
+        <v>3.957327920718549e-15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04218794387809764</v>
+        <v>-1.912393470583124e-15</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09289686075877715</v>
+        <v>0.4152352433975907</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01510175251684132</v>
+        <v>0.0002628333813758459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001919985993332374</v>
+        <v>-0.001524580256359649</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6699322291455302</v>
+        <v>0.01984301441404139</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01099734247492779</v>
+        <v>-7.661647539625372e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>0.026868861027269</v>
+        <v>-3.039577922999708e-18</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0235805461863683</v>
+        <v>-0.009271387247793375</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2152460915051791</v>
+        <v>1.233844794623437e-16</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2247589975067503</v>
+        <v>-2.956146989154017e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.160887968413964</v>
+        <v>-0.08067056442442368</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.003177682869172221</v>
+        <v>0.06746985277705521</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.541392481946109</v>
+        <v>0.2899690884799612</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00255400092970276</v>
+        <v>0.1897025964159604</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3459967911920073</v>
+        <v>2.841520316624998e-15</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4195138051584595</v>
+        <v>-2.12823317796778e-15</v>
       </c>
       <c r="X6" t="n">
-        <v>3.330779950395974</v>
+        <v>-0.4464975229430477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3714016524683519</v>
+        <v>1.966162560765759e-15</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.17029806960938</v>
+        <v>-1.086164613536816e-15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.959592648853654</v>
+        <v>-0.1572668480665227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.1340973179705463</v>
+        <v>4.676118570488777e-18</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.103833856217659</v>
+        <v>8.625690341707729e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0568663329187504</v>
+        <v>-2.874843147613061e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2671544752770684</v>
+        <v>0.4376621253113825</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02995141294299219</v>
+        <v>-3.157797440379332e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>0.117836380052036</v>
+        <v>3.957327920718541e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2998021335709599</v>
+        <v>0.1430229448017653</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.04423089414728601</v>
+        <v>2.233816682991804e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04421402633382154</v>
+        <v>-4.956609524238502e-17</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02315524691497832</v>
+        <v>2.727257329608205e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3255801061502186</v>
+        <v>1.129571509414952e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1263729009592731</v>
+        <v>-2.953590527484684e-17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03909377629280562</v>
+        <v>0.009978933203360492</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1116984789471458</v>
+        <v>-1.418763668509268e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01673715769348304</v>
+        <v>1.173700911047802e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4338944709205325</v>
+        <v>0.008409577471523301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1582014308906845</v>
+        <v>1.839732069200956e-16</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0660989982664439</v>
+        <v>6.911487966406049e-16</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.073135626049667</v>
+        <v>-2.290004478754761e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06837994045107874</v>
+        <v>-1.484789642213299e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1410476084206084</v>
+        <v>-5.945945227135957e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03567350275007232</v>
+        <v>0.04319318511589601</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02977567495134125</v>
+        <v>1.1538811284587e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03693212479203911</v>
+        <v>2.481828301047753e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1971537113044335</v>
+        <v>0.05070625926063758</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.007874901825735955</v>
+        <v>5.107206273553863e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.154325305033654</v>
+        <v>7.422117542355809e-16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.07398266543704782</v>
+        <v>8.803788737159248e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.09331776170357003</v>
+        <v>-7.231842128405855e-17</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0985247632580889</v>
+        <v>2.837392631988953e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02436939411494164</v>
+        <v>3.612703095021173e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3352027858612803</v>
+        <v>0.4376621253113822</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04218794387809781</v>
+        <v>-1.912393470583122e-15</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.04423089414728601</v>
+        <v>2.233816682991804e-16</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2126300965181891</v>
+        <v>0.1430229448017657</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0227241454790963</v>
+        <v>-6.800170510651974e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.01122028636929727</v>
+        <v>1.302934076780943e-17</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7159033823745661</v>
+        <v>-2.069300806596466e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5710402794724226</v>
+        <v>-3.016616565043583e-17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2730272557697068</v>
+        <v>5.117359406604896e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3595807143333098</v>
+        <v>0.009978933203360751</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4013542245627923</v>
+        <v>-6.609435577485421e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.04114849708239793</v>
+        <v>4.885146641146722e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1453093543329217</v>
+        <v>0.008409577471523559</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.030240134340809</v>
+        <v>-4.268651311508884e-16</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002490278289474556</v>
+        <v>8.24863212068459e-17</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4089003556476137</v>
+        <v>4.055425597086786e-16</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4523065077777619</v>
+        <v>1.246074753346391e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08356384241569548</v>
+        <v>1.317828186369678e-15</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1402160432678335</v>
+        <v>0.04319318511589812</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2853037065911365</v>
+        <v>-8.898295177029086e-16</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1362071837957134</v>
+        <v>6.250833465720376e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.05852484776823919</v>
+        <v>0.05070625926063839</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.9842143876026266</v>
+        <v>-8.54908327031768e-16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.2209550199877434</v>
+        <v>0.00758386972133346</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.436010467007104</v>
+        <v>0.01231159413127014</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.8606167382878839</v>
+        <v>0.0462778526514461</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0015740274296464</v>
+        <v>1.513161191880391e-15</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.004951809219133992</v>
+        <v>-1.862977378644034e-15</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09289686075877736</v>
+        <v>0.4152352433975907</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04421402633382159</v>
+        <v>-4.956609524238483e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.02272414547909629</v>
+        <v>-6.800170510651975e-16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2439224695399947</v>
+        <v>0.211521570882717</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1736506225982426</v>
+        <v>0.01764313544986421</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5737972046213413</v>
+        <v>0.05967647043947986</v>
       </c>
       <c r="L9" t="n">
-        <v>2.660963287089332</v>
+        <v>0.07079257724189325</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1649554190616011</v>
+        <v>1.050252934013578e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1632421619841654</v>
+        <v>-2.821195223598736e-16</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4846740809052856</v>
+        <v>-0.07439687718909667</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3927301402936784</v>
+        <v>5.051104442888832e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6586422515907684</v>
+        <v>-1.814784305912585e-16</v>
       </c>
       <c r="R9" t="n">
-        <v>7.467035434677364</v>
+        <v>-0.1106878389884163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3629609343556481</v>
+        <v>0.384730948795622</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.946823781342466</v>
+        <v>0.2070334500252858</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.43551010255412</v>
+        <v>0.1573316751831084</v>
       </c>
       <c r="V9" t="n">
-        <v>0.447332269023948</v>
+        <v>8.624618311010118e-16</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3863315273073227</v>
+        <v>-8.57354383614665e-16</v>
       </c>
       <c r="X9" t="n">
-        <v>1.477619924045569</v>
+        <v>-0.172908530404847</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4430089848808493</v>
+        <v>4.021546321404038e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.5422915964793452</v>
+        <v>-3.450208516951406e-16</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3103449010073872</v>
+        <v>-0.05360146055834362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.04328927832703033</v>
+        <v>2.277793963904295e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02872242804301314</v>
+        <v>6.180821462039763e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.03388596415441436</v>
+        <v>0.004361067254289369</v>
       </c>
       <c r="D10" t="n">
-        <v>0.020148299263587</v>
+        <v>-1.137027338551817e-17</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03767921008082038</v>
+        <v>6.117445103472972e-17</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01510175251684135</v>
+        <v>0.000262833381375846</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0231552469149783</v>
+        <v>2.727257329608203e-17</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01122028636929727</v>
+        <v>1.302934076780944e-17</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1736506225982426</v>
+        <v>0.01764313544986422</v>
       </c>
       <c r="J10" t="n">
-        <v>2.559776390741556</v>
+        <v>4.892897641955329</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1551461470250914</v>
+        <v>0.6020427689199876</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1466003847044952</v>
+        <v>0.5509422834429192</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07692582381210565</v>
+        <v>3.369620129559019e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1076378609332797</v>
+        <v>-7.285592988543995e-17</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02509899778029035</v>
+        <v>-0.01091389890915929</v>
       </c>
       <c r="P10" t="n">
-        <v>0.07108514396141527</v>
+        <v>-2.163864265845953e-17</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.16201935484581</v>
+        <v>1.183715604822857e-17</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1399505593140025</v>
+        <v>-0.007578922950445894</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0349707317840664</v>
+        <v>0.0007840850690435032</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1497659638876916</v>
+        <v>0.09247052547881407</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05427046902911392</v>
+        <v>0.1801314987180108</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1161924861022333</v>
+        <v>-2.834107188960351e-16</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1936123998028958</v>
+        <v>2.055058311315414e-16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.202332038220948</v>
+        <v>0.1815722857110159</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.109882567019687</v>
+        <v>-8.487132748131886e-17</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.01192236380962837</v>
+        <v>6.023827293227171e-17</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.5485262843499426</v>
+        <v>0.3123249654724533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.03724049206029548</v>
+        <v>6.180821462041183e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.04797128363389092</v>
+        <v>0.001107141381953379</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4404924893086686</v>
+        <v>0.01956225489473865</v>
       </c>
       <c r="D11" t="n">
-        <v>1.042983688310031e-05</v>
+        <v>9.342625539767428e-17</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01198441457787412</v>
+        <v>-8.717649081747891e-19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00191998599333229</v>
+        <v>-0.00152458025635965</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3255801061502185</v>
+        <v>1.129571509414954e-16</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7159033823745662</v>
+        <v>-2.069300806596464e-16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5737972046213411</v>
+        <v>0.05967647043947984</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1551461470250914</v>
+        <v>0.6020427689199881</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4579624100746851</v>
+        <v>1.136245798867493</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1118980518177457</v>
+        <v>0.7882964655447107</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1190286776524328</v>
+        <v>-2.177941710903223e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.00706560709110042</v>
+        <v>7.683914668691754e-16</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1992596745426842</v>
+        <v>-0.02575375726566051</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.04607537279012264</v>
+        <v>-3.347808366891393e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.04977086925797988</v>
+        <v>2.011854940651165e-16</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1951661314143814</v>
+        <v>-0.0123025017987102</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09304348191377101</v>
+        <v>0.02805835971472771</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6618264414038705</v>
+        <v>0.241286003484893</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5662537637053459</v>
+        <v>0.3255764581112043</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4836004603135649</v>
+        <v>2.505227853843419e-15</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6745133220491555</v>
+        <v>-1.304562247575277e-15</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.093844038241848</v>
+        <v>0.3794445375539867</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1188825976930062</v>
+        <v>6.381718564684414e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3757052065289835</v>
+        <v>6.491623686141709e-18</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.329727154507705</v>
+        <v>0.5029778215237183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.05747273379986541</v>
+        <v>0.004361067254289348</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4750539649665779</v>
+        <v>0.01956225489473926</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1235116163855061</v>
+        <v>0.03208826254075772</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1258493323505711</v>
+        <v>-2.803182876057982e-17</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1532876190780578</v>
+        <v>1.823458690930494e-16</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6699322291455301</v>
+        <v>0.01984301441404139</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1263729009592731</v>
+        <v>-2.953590527484585e-17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5710402794724226</v>
+        <v>-3.016616565043651e-17</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66096328708933</v>
+        <v>0.07079257724189326</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1466003847044949</v>
+        <v>0.5509422834429192</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1118980518177475</v>
+        <v>0.7882964655447106</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9898152988092557</v>
+        <v>0.5646529090313909</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09737800460879353</v>
+        <v>-8.314489829454551e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05022453679074389</v>
+        <v>2.246349166833899e-16</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3315562477207302</v>
+        <v>-0.06667011286309657</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.006442139959555643</v>
+        <v>-1.354245747056415e-16</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00110899242197926</v>
+        <v>1.147140928180091e-16</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8375763207770335</v>
+        <v>-0.04608884630288274</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1807331542966702</v>
+        <v>0.1741267691783684</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.633045142135169</v>
+        <v>0.2027236723366802</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.601650907194186</v>
+        <v>0.2550843692736618</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02808600165576955</v>
+        <v>1.10487021022716e-15</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1271902983050405</v>
+        <v>-5.160023992588327e-16</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.492815466875181</v>
+        <v>0.2807945045099997</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0003867658997993573</v>
+        <v>2.41573570985293e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.04394511397550993</v>
+        <v>1.367594521940176e-16</v>
       </c>
       <c r="AA12" t="n">
-        <v>-2.209143203404286</v>
+        <v>0.3516652824967392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01438312874804778</v>
+        <v>-3.397842551698439e-17</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.02665035994122673</v>
+        <v>1.57532758909217e-16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1324986389563613</v>
+        <v>8.421612013601298e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06384140613802622</v>
+        <v>-0.0001311157213853492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01155220301451596</v>
+        <v>-2.478403481261463e-16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01099734247492778</v>
+        <v>-7.661647539625363e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.03909377629280562</v>
+        <v>0.009978933203360496</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2730272557697067</v>
+        <v>5.117359406604894e-16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1649554190616011</v>
+        <v>1.050252934013578e-15</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07692582381210565</v>
+        <v>3.369620129559043e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1190286776524328</v>
+        <v>-2.177941710903221e-15</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.09737800460879351</v>
+        <v>-8.314489829454543e-16</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5961599537790052</v>
+        <v>1.191024825962523</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1204601890429589</v>
+        <v>-1.319638375443824e-15</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01896619295663794</v>
+        <v>-1.048098519045619e-14</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2129489672548815</v>
+        <v>0.4378130917326574</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.04213025238886331</v>
+        <v>6.016294178300968e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>0.04349082956845973</v>
+        <v>-8.807983829848874e-15</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07073476385981425</v>
+        <v>-2.584785212029677e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1571351373104556</v>
+        <v>1.744364857432544e-15</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2658634213724857</v>
+        <v>1.023035054805016e-15</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2025015486014489</v>
+        <v>0.1137034046467892</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2170838249720593</v>
+        <v>2.552431707371661e-15</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4431876117659879</v>
+        <v>-5.121282968712052e-15</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.002355680071254543</v>
+        <v>0.144338292161474</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3368017147838947</v>
+        <v>1.136722225820409e-15</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.01935864227917947</v>
+        <v>-4.91108500308062e-15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.04793011673866257</v>
+        <v>-2.552522888200456e-18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02049980313820794</v>
+        <v>2.375682626075278e-17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1874553085332433</v>
+        <v>-7.767699621681552e-17</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03239423413150068</v>
+        <v>3.359394555427063e-17</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03934127170063006</v>
+        <v>-0.0001311157213856174</v>
       </c>
       <c r="F14" t="n">
-        <v>0.026868861027269</v>
+        <v>-3.039577922999701e-18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1116984789471458</v>
+        <v>-1.418763668509268e-16</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3595807143333097</v>
+        <v>0.009978933203360752</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1632421619841654</v>
+        <v>-2.821195223598735e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1076378609332797</v>
+        <v>-7.285592988543967e-17</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.007065607091100476</v>
+        <v>7.683914668691756e-16</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05022453679074397</v>
+        <v>2.246349166833906e-16</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1204601890429589</v>
+        <v>-1.319638375443824e-15</v>
       </c>
       <c r="N14" t="n">
-        <v>0.429959393963034</v>
+        <v>1.191024825962522</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1223067705290536</v>
+        <v>-4.834494402823264e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1415541976626938</v>
+        <v>-3.497700990479528e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2216974110687461</v>
+        <v>0.4378130917326572</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.00484654616929211</v>
+        <v>1.184101487146061e-15</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0380367428542126</v>
+        <v>-5.466642736909423e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4230659291664233</v>
+        <v>-8.399154813701662e-16</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03332009187427507</v>
+        <v>-3.427854697205191e-16</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2443410447201789</v>
+        <v>-2.703582589645091e-16</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.05372070193429737</v>
+        <v>0.1137034046467922</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4495950769629764</v>
+        <v>-5.426631478700654e-16</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1733919514998904</v>
+        <v>-1.815542495463897e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2419587199412605</v>
+        <v>0.1443382921614743</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1790713917819428</v>
+        <v>4.463615971472972e-16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.02078350983047048</v>
+        <v>-0.000340524163401378</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05573856886858201</v>
+        <v>0.000779533199925328</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8825511133401214</v>
+        <v>-0.02090546578538786</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.002568101092617355</v>
+        <v>1.122219968897037e-15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05185808020567101</v>
+        <v>-4.184121362838133e-16</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02358054618636827</v>
+        <v>-0.009271387247793387</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01673715769348305</v>
+        <v>1.173700911047803e-15</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4013542245627924</v>
+        <v>-6.609435577485417e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.484674080905286</v>
+        <v>-0.07439687718909663</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02509899778029033</v>
+        <v>-0.01091389890915924</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1992596745426841</v>
+        <v>-0.02575375726566045</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3315562477207304</v>
+        <v>-0.06667011286309656</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01896619295663796</v>
+        <v>-1.048098519045618e-14</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1223067705290536</v>
+        <v>-4.83449440282326e-16</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4368534629209373</v>
+        <v>1.039251202443088</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06297290253979139</v>
+        <v>-1.709340736811642e-15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06136687677283039</v>
+        <v>-9.370556832228718e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03357564456713723</v>
+        <v>0.4152547254439395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.06253913715770014</v>
+        <v>-0.0672373461829211</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8875865358414435</v>
+        <v>-0.2897613552996052</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1578059003903523</v>
+        <v>-0.1895995621106739</v>
       </c>
       <c r="V15" t="n">
-        <v>0.006553005688697086</v>
+        <v>5.407272537082234e-15</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4094931920805067</v>
+        <v>-3.76880785456763e-15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.835790979388002</v>
+        <v>-0.4448961699489076</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1821002273832631</v>
+        <v>1.675945387654658e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.3732416647863951</v>
+        <v>-1.490196332373673e-15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.454086692486809</v>
+        <v>-0.1562256354480017</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.007514102544864022</v>
+        <v>-1.373830487826967e-17</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3413649377313676</v>
+        <v>-6.245707984660764e-17</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3890245181911434</v>
+        <v>2.48145403153303e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1705338143143498</v>
+        <v>0.01079237245975019</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1305030129462645</v>
+        <v>4.806723473979157e-16</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2152460915051792</v>
+        <v>1.233844794623439e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4338944709205326</v>
+        <v>0.008409577471523301</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.04114849708239791</v>
+        <v>4.885146641146723e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3927301402936786</v>
+        <v>5.051104442888827e-16</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07108514396141527</v>
+        <v>-2.163864265845847e-17</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04607537279012261</v>
+        <v>-3.347808366891383e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.006442139959555532</v>
+        <v>-1.354245747056448e-16</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2129489672548815</v>
+        <v>0.4378130917326575</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1415541976626938</v>
+        <v>-3.49770099047953e-16</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06297290253979136</v>
+        <v>-1.709340736811642e-15</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2568217131712441</v>
+        <v>0.1431209841693558</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04370180008433452</v>
+        <v>3.405458763754786e-16</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0488388921586144</v>
+        <v>-2.336615803103468e-15</v>
       </c>
       <c r="S16" t="n">
-        <v>0.04818092515576727</v>
+        <v>-1.697406369097807e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1169252807846761</v>
+        <v>3.039397228271346e-16</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1713676256734851</v>
+        <v>2.520063900823526e-16</v>
       </c>
       <c r="V16" t="n">
-        <v>0.02509199468962441</v>
+        <v>0.0432523361770158</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1080358716043331</v>
+        <v>1.313533409624755e-15</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4499433205242608</v>
+        <v>-2.899685644282149e-15</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1957103392868409</v>
+        <v>0.0509889340191863</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1272072262122085</v>
+        <v>6.524779255080973e-16</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.5604429974200316</v>
+        <v>-1.798254687057362e-15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.04260902357998274</v>
+        <v>2.786025309177214e-18</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8196874487134383</v>
+        <v>9.99763461728153e-17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.006243368851932496</v>
+        <v>3.225396626733719e-17</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08641481815868828</v>
+        <v>5.093672435854774e-16</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5093852048291789</v>
+        <v>0.01079237245975032</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2247589975067505</v>
+        <v>-2.956146989154016e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1582014308906845</v>
+        <v>1.839732069200956e-16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1453093543329217</v>
+        <v>0.008409577471523561</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6586422515907681</v>
+        <v>-1.814784305912586e-16</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.16201935484581</v>
+        <v>1.183715604822855e-17</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.04977086925797977</v>
+        <v>2.011854940651164e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00110899242197926</v>
+        <v>1.147140928180092e-16</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.04213025238886328</v>
+        <v>6.016294178300967e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2216974110687461</v>
+        <v>0.4378130917326571</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06136687677283041</v>
+        <v>-9.370556832228718e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0437018000843345</v>
+        <v>3.405458763754786e-16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2533249443516369</v>
+        <v>0.1431209841693556</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.00303773914465606</v>
+        <v>5.745889693566162e-17</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.01449947237915819</v>
+        <v>5.52797777969674e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3906989825138306</v>
+        <v>-6.264432611438024e-17</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5229104250473664</v>
+        <v>3.127317241286183e-17</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01317447425773871</v>
+        <v>2.89336625863631e-16</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01726710930167755</v>
+        <v>0.0432523361770173</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4784684597539604</v>
+        <v>4.193729461825775e-16</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.06210840641123374</v>
+        <v>2.589004403655597e-16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.190716029879426</v>
+        <v>0.0509889340191865</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6073776678783043</v>
+        <v>2.50650741551282e-16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.149787302087932</v>
+        <v>-0.01792337552459341</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.6049677143131579</v>
+        <v>-0.0653639768085742</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.148854857467975</v>
+        <v>-0.06971860414654685</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08298628647109868</v>
+        <v>9.67840104559982e-16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0400314500908914</v>
+        <v>-5.316011823962526e-16</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.160887968413964</v>
+        <v>-0.08067056442442364</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0660989982664439</v>
+        <v>6.911487966406047e-16</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.030240134340809</v>
+        <v>-4.268651311508887e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>7.467035434677366</v>
+        <v>-0.1106878389884164</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1399505593140023</v>
+        <v>-0.007578922950445884</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1951661314143803</v>
+        <v>-0.01230250179871017</v>
       </c>
       <c r="L18" t="n">
-        <v>0.837576320777034</v>
+        <v>-0.04608884630288275</v>
       </c>
       <c r="M18" t="n">
-        <v>0.04349082956845973</v>
+        <v>-8.807983829848874e-15</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.004846546169292075</v>
+        <v>1.184101487146062e-15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0335756445671373</v>
+        <v>0.4152547254439394</v>
       </c>
       <c r="P18" t="n">
-        <v>0.04883889215861442</v>
+        <v>-2.33661580310347e-15</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.003037739144656016</v>
+        <v>5.745889693566194e-17</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.2278332991578863</v>
+        <v>0.2105623812905677</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1440848702510136</v>
+        <v>-0.3824587934032586</v>
       </c>
       <c r="T18" t="n">
-        <v>2.391721884395471</v>
+        <v>-0.2049736596350795</v>
       </c>
       <c r="U18" t="n">
-        <v>1.735380972413801</v>
+        <v>-0.1561249853551838</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.01167666975947611</v>
+        <v>2.776502182116074e-15</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2745368285105038</v>
+        <v>-1.797342179294607e-15</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4763806032929335</v>
+        <v>-0.1662035540232444</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.06298459582954752</v>
+        <v>6.169648939370136e-16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3800604435737475</v>
+        <v>-5.407242939561736e-16</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.2720029557827545</v>
+        <v>-0.05166214186233484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.01722100174373187</v>
+        <v>0.0007840850690434845</v>
       </c>
       <c r="B19" t="n">
-        <v>0.04005452720909844</v>
+        <v>0.02805835971472784</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2128292681003967</v>
+        <v>0.1741267691783683</v>
       </c>
       <c r="D19" t="n">
-        <v>0.009347721661147527</v>
+        <v>-7.104945111132761e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05836804347281759</v>
+        <v>1.968867188832426e-16</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.003177682869172083</v>
+        <v>0.06746985277705522</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07313562604966699</v>
+        <v>-2.29000447875476e-16</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002490278289474583</v>
+        <v>8.248632120684609e-17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3629609343556479</v>
+        <v>0.384730948795622</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.03497073178406641</v>
+        <v>0.0007840850690435037</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09304348191377096</v>
+        <v>0.02805835971472771</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18073315429667</v>
+        <v>0.1741267691783684</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07073476385981424</v>
+        <v>-2.584785212029675e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03803674285421259</v>
+        <v>-5.466642736909426e-17</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06253913715770036</v>
+        <v>-0.06723734618292108</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04818092515576726</v>
+        <v>-1.697406369097807e-16</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.01449947237915823</v>
+        <v>5.527977779696742e-17</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1440848702510138</v>
+        <v>-0.3824587934032588</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9665211342102418</v>
+        <v>3.557256355787352</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2753819875551748</v>
+        <v>0.3849543821651945</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1463741414735854</v>
+        <v>0.4305348720512637</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0353191329907453</v>
+        <v>-8.335843405471596e-17</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1238600376698312</v>
+        <v>1.852487563144764e-17</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1210985444038304</v>
+        <v>0.0003128781032646394</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.008776952526654475</v>
+        <v>-1.481301198503847e-16</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.08487437172779527</v>
+        <v>-4.879178447897005e-17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1008569635445457</v>
+        <v>0.0003756858818615495</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.05284167274159016</v>
+        <v>0.09247052547881411</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7103312281000539</v>
+        <v>0.241286003484896</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.7585243655546633</v>
+        <v>0.2027236723366815</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1280226980225189</v>
+        <v>-3.247762197431187e-15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3361638313409374</v>
+        <v>1.031565610655227e-15</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.541392481946109</v>
+        <v>0.2899690884799612</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06837994045107865</v>
+        <v>-1.484789642213299e-15</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4089003556476137</v>
+        <v>4.055425597086791e-16</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.946823781342464</v>
+        <v>0.2070334500252859</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1497659638876916</v>
+        <v>0.09247052547881406</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6618264414038717</v>
+        <v>0.241286003484893</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.63304514213517</v>
+        <v>0.2027236723366802</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1571351373104557</v>
+        <v>1.744364857432541e-15</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4230659291664233</v>
+        <v>-8.399154813701653e-16</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8875865358414444</v>
+        <v>-0.2897613552996051</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1169252807846761</v>
+        <v>3.039397228271333e-16</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3906989825138308</v>
+        <v>-6.264432611438042e-17</v>
       </c>
       <c r="R20" t="n">
-        <v>2.391721884395472</v>
+        <v>-0.2049736596350796</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2753819875551744</v>
+        <v>0.3849543821651946</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.596037958947849</v>
+        <v>0.2937405502998858</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.199659716518652</v>
+        <v>0.261125921198073</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.06643720840933313</v>
+        <v>-1.577677205882151e-15</v>
       </c>
       <c r="W20" t="n">
-        <v>0.03622766620909351</v>
+        <v>6.591128722338825e-16</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5195223865608801</v>
+        <v>0.0004586971556489592</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.03989487785367306</v>
+        <v>-7.947159014693963e-16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04188539132208546</v>
+        <v>3.216938729515436e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.09788832099659195</v>
+        <v>0.0009190270871363756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.1751108644916988</v>
+        <v>0.1801314987180109</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.4776895950143697</v>
+        <v>0.3255764581112065</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.555173260730673</v>
+        <v>0.2550843692736626</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06995697083609853</v>
+        <v>-1.454720075916617e-15</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1414267378950517</v>
+        <v>3.915137501783901e-16</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002554000929702038</v>
+        <v>0.1897025964159604</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1410476084206084</v>
+        <v>-5.945945227135952e-16</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4523065077777615</v>
+        <v>1.246074753346389e-16</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.435510102554121</v>
+        <v>0.1573316751831085</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05427046902911398</v>
+        <v>0.180131498718011</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5662537637053441</v>
+        <v>0.3255764581112044</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.601650907194186</v>
+        <v>0.2550843692736619</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2658634213724857</v>
+        <v>1.023035054805021e-15</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.03332009187427502</v>
+        <v>-3.427854697205195e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1578059003903517</v>
+        <v>-0.1895995621106738</v>
       </c>
       <c r="P21" t="n">
-        <v>0.171367625673485</v>
+        <v>2.52006390082351e-16</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.522910425047366</v>
+        <v>3.127317241286176e-17</v>
       </c>
       <c r="R21" t="n">
-        <v>1.735380972413803</v>
+        <v>-0.1561249853551838</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1463741414735856</v>
+        <v>0.4305348720512638</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.199659716518652</v>
+        <v>0.2611259211980732</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.653883121630652</v>
+        <v>0.2698162708261449</v>
       </c>
       <c r="V21" t="n">
-        <v>0.05527267590342473</v>
+        <v>-5.962608962404225e-16</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.07140308902449477</v>
+        <v>2.575774846534283e-16</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5498892989272504</v>
+        <v>0.0003555602966190507</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1035524945935813</v>
+        <v>-2.753808411011512e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.09601505712293779</v>
+        <v>1.657679104178384e-16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1842001616268312</v>
+        <v>0.0008229058200327831</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.09857334360723925</v>
+        <v>4.44013549193938e-17</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.8434180300837161</v>
+        <v>-6.482093157361339e-16</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6841530643549898</v>
+        <v>-4.626781688552997e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.08988831917730876</v>
+        <v>0.1135229257250884</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2624065950466219</v>
+        <v>2.389715389611256e-15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3459967911920073</v>
+        <v>2.841520316624998e-15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03567350275007233</v>
+        <v>0.04319318511589601</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08356384241569548</v>
+        <v>1.317828186369678e-15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4473322690239473</v>
+        <v>8.62461831101012e-16</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1161924861022333</v>
+        <v>-2.834107188960352e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4836004603135647</v>
+        <v>2.505227853843419e-15</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.02808600165576949</v>
+        <v>1.104870210227162e-15</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.202501548601449</v>
+        <v>0.1137034046467893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2443410447201789</v>
+        <v>-2.703582589645091e-16</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00655300568869692</v>
+        <v>5.407272537082233e-15</v>
       </c>
       <c r="P22" t="n">
-        <v>0.02509199468962443</v>
+        <v>0.04325233617701579</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0131744742577387</v>
+        <v>2.89336625863631e-16</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.01167666975947614</v>
+        <v>2.776502182116074e-15</v>
       </c>
       <c r="S22" t="n">
-        <v>0.03531913299074526</v>
+        <v>-8.3358434054716e-17</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.06643720840933311</v>
+        <v>-1.577677205882151e-15</v>
       </c>
       <c r="U22" t="n">
-        <v>0.05527267590342473</v>
+        <v>-5.962608962404231e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3581977065503137</v>
+        <v>0.03915084183676932</v>
       </c>
       <c r="W22" t="n">
-        <v>0.08803258970993719</v>
+        <v>1.983105333258997e-15</v>
       </c>
       <c r="X22" t="n">
-        <v>0.06278619231606697</v>
+        <v>-4.843109055072023e-15</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2440936177323621</v>
+        <v>0.03683450504784625</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.01348713155686793</v>
+        <v>1.08747658376026e-15</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.3154825939227565</v>
+        <v>-2.131243306990414e-16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1340388185222632</v>
+        <v>-1.162737942979771e-17</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.1356721416658286</v>
+        <v>5.768805169174933e-16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.4648977372355639</v>
+        <v>3.527770665191417e-16</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07497279927591531</v>
+        <v>2.427842827781269e-15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3676672279970428</v>
+        <v>0.1135229257250923</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4195138051584592</v>
+        <v>-2.128233177967782e-15</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02977567495134125</v>
+        <v>1.1538811284587e-15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1402160432678335</v>
+        <v>0.04319318511589811</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3863315273073227</v>
+        <v>-8.573543836146655e-16</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1936123998028958</v>
+        <v>2.055058311315416e-16</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6745133220491555</v>
+        <v>-1.304562247575277e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1271902983050405</v>
+        <v>-5.160023992588325e-16</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2170838249720594</v>
+        <v>2.55243170737166e-15</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0537207019342973</v>
+        <v>0.1137034046467922</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4094931920805068</v>
+        <v>-3.768807854567631e-15</v>
       </c>
       <c r="P23" t="n">
-        <v>0.108035871604333</v>
+        <v>1.313533409624754e-15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.01726710930167756</v>
+        <v>0.04325233617701731</v>
       </c>
       <c r="R23" t="n">
-        <v>0.274536828510504</v>
+        <v>-1.797342179294607e-15</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1238600376698312</v>
+        <v>1.852487563144756e-17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.03622766620909344</v>
+        <v>6.591128722338826e-16</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.07140308902449477</v>
+        <v>2.575774846534275e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>0.08803258970993716</v>
+        <v>1.983105333258997e-15</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3330641559685905</v>
+        <v>0.03915084183677329</v>
       </c>
       <c r="X23" t="n">
-        <v>0.03535821993102417</v>
+        <v>2.868931943944592e-15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.05356941604812628</v>
+        <v>1.303241390500077e-15</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1788339063092444</v>
+        <v>0.03683450504784841</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.09259653551755159</v>
+        <v>-2.855469892785458e-16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.267853816709839</v>
+        <v>-0.1815834160200568</v>
       </c>
       <c r="B24" t="n">
-        <v>4.679948070618551</v>
+        <v>-0.3794276433736797</v>
       </c>
       <c r="C24" t="n">
-        <v>2.357502712755822</v>
+        <v>-0.2801140382758386</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04652939776438733</v>
+        <v>8.394861729787418e-15</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6532567243171629</v>
+        <v>-3.591005271356497e-15</v>
       </c>
       <c r="F24" t="n">
-        <v>3.330779950395971</v>
+        <v>-0.4464975229430477</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03693212479203903</v>
+        <v>2.481828301047755e-15</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2853037065911367</v>
+        <v>-8.898295177029082e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>1.477619924045568</v>
+        <v>-0.172908530404847</v>
       </c>
       <c r="J24" t="n">
-        <v>1.202332038220949</v>
+        <v>0.1815722857110159</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.093844038241846</v>
+        <v>0.3794445375539864</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.492815466875185</v>
+        <v>0.2807945045099998</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4431876117659876</v>
+        <v>-5.121282968712055e-15</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4495950769629765</v>
+        <v>-5.426631478700658e-16</v>
       </c>
       <c r="O24" t="n">
-        <v>1.835790979388</v>
+        <v>-0.4448961699489076</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4499433205242609</v>
+        <v>-2.899685644282148e-15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4784684597539604</v>
+        <v>4.193729461825782e-16</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4763806032929349</v>
+        <v>-0.1662035540232444</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1210985444038305</v>
+        <v>0.0003128781032646181</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5195223865608787</v>
+        <v>0.0004586971556490335</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5498892989272499</v>
+        <v>0.0003555602966190039</v>
       </c>
       <c r="V24" t="n">
-        <v>0.06278619231606691</v>
+        <v>-4.843109055072024e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>0.03535821993102428</v>
+        <v>2.868931943944592e-15</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4001208360152164</v>
+        <v>0.6963487637026637</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.09418716433261423</v>
+        <v>-1.348299429760757e-15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.01495289493199825</v>
+        <v>3.035911428167399e-16</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.4776837484155951</v>
+        <v>0.4540604789867984</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.0561435912350044</v>
+        <v>2.239209142907611e-17</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.08099713667798122</v>
+        <v>3.112702011111814e-16</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1855838638663503</v>
+        <v>6.783164846643296e-17</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05558051159775829</v>
+        <v>0.1439004977286861</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3124212471220639</v>
+        <v>8.176479522531828e-16</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3714016524683517</v>
+        <v>1.96616256076576e-15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1971537113044336</v>
+        <v>0.05070625926063758</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1362071837957134</v>
+        <v>6.250833465720374e-16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4430089848808493</v>
+        <v>4.02154632140404e-16</v>
       </c>
       <c r="J25" t="n">
-        <v>0.109882567019687</v>
+        <v>-8.487132748131893e-17</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1188825976930062</v>
+        <v>6.381718564684422e-16</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0003867658997993573</v>
+        <v>2.415735709852932e-16</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.002355680071254529</v>
+        <v>0.144338292161474</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1733919514998904</v>
+        <v>-1.815542495463897e-16</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1821002273832633</v>
+        <v>1.675945387654657e-15</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1957103392868409</v>
+        <v>0.05098893401918631</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0621084064112337</v>
+        <v>2.589004403655596e-16</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06298459582954752</v>
+        <v>6.169648939370138e-16</v>
       </c>
       <c r="S25" t="n">
-        <v>0.008776952526654482</v>
+        <v>-1.481301198503846e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0398948778536731</v>
+        <v>-7.947159014693963e-16</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1035524945935813</v>
+        <v>-2.753808411011504e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2440936177323621</v>
+        <v>0.03683450504784625</v>
       </c>
       <c r="W25" t="n">
-        <v>0.05356941604812628</v>
+        <v>1.303241390500077e-15</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.09418716433261423</v>
+        <v>-1.348299429760757e-15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.2757725318631968</v>
+        <v>0.0356418607612326</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.02902248536181955</v>
+        <v>6.692991632766927e-16</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.09353547539926588</v>
+        <v>-3.203358204517286e-16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.02060803788629979</v>
+        <v>2.803191920560953e-17</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0842715549067401</v>
+        <v>-6.353841898545101e-17</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1735964690947602</v>
+        <v>3.557803605218277e-17</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1130759083614428</v>
+        <v>1.087915168824748e-15</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4130051094565371</v>
+        <v>0.1439004977286873</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1702980696093798</v>
+        <v>-1.086164613536816e-15</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.007874901825735955</v>
+        <v>5.107206273553864e-16</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05852484776823919</v>
+        <v>0.05070625926063839</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5422915964793458</v>
+        <v>-3.45020851695141e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0119223638096283</v>
+        <v>6.023827293227169e-17</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3757052065289835</v>
+        <v>6.491623686141018e-18</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04394511397550993</v>
+        <v>1.367594521940173e-16</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3368017147838948</v>
+        <v>1.13672222582041e-15</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2419587199412606</v>
+        <v>0.1443382921614743</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3732416647863951</v>
+        <v>-1.490196332373673e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1272072262122085</v>
+        <v>6.524779255080971e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.190716029879426</v>
+        <v>0.05098893401918651</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3800604435737476</v>
+        <v>-5.407242939561742e-16</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.08487437172779527</v>
+        <v>-4.879178447897001e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>0.04188539132208542</v>
+        <v>3.216938729515429e-16</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.09601505712293798</v>
+        <v>1.657679104178378e-16</v>
       </c>
       <c r="V26" t="n">
-        <v>0.01348713155686793</v>
+        <v>1.08747658376026e-15</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1788339063092444</v>
+        <v>0.0368345050478484</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01495289493199831</v>
+        <v>3.035911428167392e-16</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.02902248536181959</v>
+        <v>6.692991632766925e-16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.06019710827298222</v>
+        <v>0.03564186076123344</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.03303747235367893</v>
+        <v>-1.275729039235028e-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.2100887004266616</v>
+        <v>-0.3123303662758078</v>
       </c>
       <c r="B27" t="n">
-        <v>2.204350177292083</v>
+        <v>-0.5029630951101126</v>
       </c>
       <c r="C27" t="n">
-        <v>2.336006789121666</v>
+        <v>-0.3500064536573369</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1399306999868982</v>
+        <v>3.288546787631618e-15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4416675868065112</v>
+        <v>-2.376062801743565e-15</v>
       </c>
       <c r="F27" t="n">
-        <v>1.959592648853654</v>
+        <v>-0.1572668480665229</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1543253050336538</v>
+        <v>7.422117542355817e-16</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9842143876026266</v>
+        <v>-8.549083270317698e-16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3103449010073885</v>
+        <v>-0.05360146055834362</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5485262843499426</v>
+        <v>0.3123249654724535</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.329727154507706</v>
+        <v>0.5029778215237179</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.209143203404283</v>
+        <v>0.3516652824967396</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.01935864227917941</v>
+        <v>-4.911085003080613e-15</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1790713917819428</v>
+        <v>4.463615971472975e-16</v>
       </c>
       <c r="O27" t="n">
-        <v>1.45408669248681</v>
+        <v>-0.1562256354480018</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.5604429974200316</v>
+        <v>-1.798254687057366e-15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6073776678783045</v>
+        <v>2.506507415512819e-16</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.272002955782755</v>
+        <v>-0.05166214186233486</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1008569635445457</v>
+        <v>0.0003756858818615246</v>
       </c>
       <c r="T27" t="n">
-        <v>0.09788832099659169</v>
+        <v>0.0009190270871363503</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1842001616268319</v>
+        <v>0.0008229058200328767</v>
       </c>
       <c r="V27" t="n">
-        <v>0.3154825939227567</v>
+        <v>-2.131243306990419e-16</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.09259653551755176</v>
+        <v>-2.855469892785469e-16</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.4776837484155938</v>
+        <v>0.4540604789867984</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.09353547539926588</v>
+        <v>-3.203358204517297e-16</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.03303747235367893</v>
+        <v>-1.275729039235027e-16</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.866420605517245</v>
+        <v>0.4677057030168582</v>
       </c>
     </row>
   </sheetData>
